--- a/원본데이터/처방현황_260620.xlsx
+++ b/원본데이터/처방현황_260620.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="89">
   <si>
     <t>등록번호</t>
   </si>
@@ -300,6 +300,24 @@
   </si>
   <si>
     <t>김현경</t>
+  </si>
+  <si>
+    <t>이영재</t>
+  </si>
+  <si>
+    <t>이천배</t>
+  </si>
+  <si>
+    <t>이헌상</t>
+  </si>
+  <si>
+    <t>강연자</t>
+  </si>
+  <si>
+    <t>(Hicardi)Bed side monitoring(1일당)</t>
+  </si>
+  <si>
+    <t>박우춘</t>
   </si>
 </sst>
 </file>
@@ -382,7 +400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -413,7 +431,22 @@
         <color rgb="FF000000"/>
       </right>
       <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -426,7 +459,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -436,9 +469,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -447,6 +477,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -727,7 +763,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:O88"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -735,13 +770,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
@@ -778,12 +813,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
+    <row r="2" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
@@ -825,12 +860,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>51</v>
+    <row r="3" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C3" t="s">
         <v>78</v>
@@ -872,12 +907,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>51</v>
+    <row r="4" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C4" t="s">
         <v>78</v>
@@ -919,12 +954,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>51</v>
+    <row r="5" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C5" t="s">
         <v>78</v>
@@ -966,12 +1001,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>51</v>
+    <row r="6" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>
@@ -1013,12 +1048,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>51</v>
+    <row r="7" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>78</v>
@@ -1060,12 +1095,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>51</v>
+    <row r="8" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C8" t="s">
         <v>78</v>
@@ -1107,12 +1142,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>51</v>
+    <row r="9" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C9" t="s">
         <v>78</v>
@@ -1154,12 +1189,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>51</v>
+    <row r="10" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>78</v>
@@ -1201,12 +1236,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>51</v>
+    <row r="11" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>78</v>
@@ -1248,12 +1283,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>51</v>
+    <row r="12" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C12" t="s">
         <v>78</v>
@@ -1295,274 +1330,274 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>51</v>
+    <row r="13" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C13" t="s">
         <v>78</v>
       </c>
       <c r="D13">
+        <v>657621</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13">
+        <v>20260619</v>
+      </c>
+      <c r="I13">
+        <v>20260620</v>
+      </c>
+      <c r="J13">
+        <v>38</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14">
         <v>685857</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>31</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>15</v>
       </c>
-      <c r="G13">
+      <c r="G14">
         <v>7</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>20260617</v>
       </c>
-      <c r="I13">
-        <v>20260620</v>
-      </c>
-      <c r="J13">
+      <c r="I14">
+        <v>20260620</v>
+      </c>
+      <c r="J14">
         <v>52</v>
       </c>
-      <c r="K13">
-        <v>1</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>1</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14">
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15">
         <v>687789</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>32</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G15" t="s">
         <v>33</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>20260615</v>
       </c>
-      <c r="I14">
-        <v>20260620</v>
-      </c>
-      <c r="J14">
+      <c r="I15">
+        <v>20260620</v>
+      </c>
+      <c r="J15">
         <v>57</v>
       </c>
-      <c r="K14">
+      <c r="K15">
         <v>3</v>
       </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-      <c r="M14">
-        <v>1</v>
-      </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D15">
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16">
         <v>721194</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>15</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>20260506</v>
       </c>
-      <c r="I15">
-        <v>20260620</v>
-      </c>
-      <c r="J15">
+      <c r="I16">
+        <v>20260620</v>
+      </c>
+      <c r="J16">
         <v>1332</v>
       </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-      <c r="M15">
-        <v>1</v>
-      </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16">
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17">
         <v>723246</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>35</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>13</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>10</v>
       </c>
-      <c r="H16">
+      <c r="H17">
         <v>20260510</v>
       </c>
-      <c r="I16">
-        <v>20260620</v>
-      </c>
-      <c r="J16">
+      <c r="I17">
+        <v>20260620</v>
+      </c>
+      <c r="J17">
         <v>1093</v>
       </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>1</v>
-      </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17">
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18">
         <v>781672</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>36</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>15</v>
-      </c>
-      <c r="G17">
-        <v>8</v>
-      </c>
-      <c r="H17">
-        <v>20260618</v>
-      </c>
-      <c r="I17">
-        <v>20260620</v>
-      </c>
-      <c r="J17">
-        <v>62</v>
-      </c>
-      <c r="K17">
-        <v>5</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17">
-        <v>1</v>
-      </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18">
-        <v>845293</v>
-      </c>
-      <c r="E18" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" t="s">
-        <v>13</v>
       </c>
       <c r="G18">
         <v>8</v>
       </c>
       <c r="H18">
-        <v>20260521</v>
+        <v>20260618</v>
       </c>
       <c r="I18">
         <v>20260620</v>
       </c>
       <c r="J18">
-        <v>276</v>
+        <v>62</v>
       </c>
       <c r="K18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L18">
         <v>1</v>
@@ -1577,262 +1612,262 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>51</v>
+    <row r="19" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C19" t="s">
         <v>78</v>
       </c>
       <c r="D19">
-        <v>867857</v>
+        <v>845293</v>
       </c>
       <c r="E19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <v>20260521</v>
+      </c>
+      <c r="I19">
+        <v>20260620</v>
+      </c>
+      <c r="J19">
+        <v>276</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19">
+        <v>1</v>
+      </c>
+      <c r="M19">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>1</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20">
+        <v>867857</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" t="s">
         <v>14</v>
       </c>
-      <c r="H19">
+      <c r="H20">
         <v>20260617</v>
       </c>
-      <c r="I19">
-        <v>20260620</v>
-      </c>
-      <c r="J19">
+      <c r="I20">
+        <v>20260620</v>
+      </c>
+      <c r="J20">
         <v>34</v>
       </c>
-      <c r="K19">
+      <c r="K20">
         <v>4</v>
       </c>
-      <c r="L19">
-        <v>1</v>
-      </c>
-      <c r="M19">
-        <v>1</v>
-      </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-      <c r="O19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20">
+      <c r="L20">
+        <v>1</v>
+      </c>
+      <c r="M20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="O20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21">
         <v>871083</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>76</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>21</v>
-      </c>
-      <c r="G20">
-        <v>8</v>
-      </c>
-      <c r="H20">
-        <v>20260618</v>
-      </c>
-      <c r="I20">
-        <v>20260620</v>
-      </c>
-      <c r="J20">
-        <v>54</v>
-      </c>
-      <c r="K20">
-        <v>6</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20">
-        <v>1</v>
-      </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21">
-        <v>873280</v>
-      </c>
-      <c r="E21" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" t="s">
-        <v>16</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21">
+        <v>20260618</v>
+      </c>
+      <c r="I21">
+        <v>20260620</v>
+      </c>
+      <c r="J21">
+        <v>54</v>
+      </c>
+      <c r="K21">
+        <v>6</v>
+      </c>
+      <c r="L21">
+        <v>1</v>
+      </c>
+      <c r="M21">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22">
+        <v>873280</v>
+      </c>
+      <c r="E22" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22">
         <v>20260616</v>
       </c>
-      <c r="I21">
-        <v>20260620</v>
-      </c>
-      <c r="J21">
+      <c r="I22">
+        <v>20260620</v>
+      </c>
+      <c r="J22">
         <v>57</v>
       </c>
-      <c r="K21">
+      <c r="K22">
         <v>7</v>
       </c>
-      <c r="L21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22">
+      <c r="L22">
+        <v>1</v>
+      </c>
+      <c r="M22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="O22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23">
         <v>873455</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>39</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>33</v>
-      </c>
-      <c r="H22">
-        <v>20260530</v>
-      </c>
-      <c r="I22">
-        <v>20260620</v>
-      </c>
-      <c r="J22">
-        <v>320</v>
-      </c>
-      <c r="K22">
-        <v>3</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
-      </c>
-      <c r="M22">
-        <v>1</v>
-      </c>
-      <c r="N22">
-        <v>1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23">
-        <v>876937</v>
-      </c>
-      <c r="E23" t="s">
-        <v>40</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23">
+        <v>20260530</v>
+      </c>
+      <c r="I23">
+        <v>20260620</v>
+      </c>
+      <c r="J23">
+        <v>320</v>
+      </c>
+      <c r="K23">
+        <v>3</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>1</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+      <c r="D24">
+        <v>876937</v>
+      </c>
+      <c r="E24" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" t="s">
         <v>14</v>
-      </c>
-      <c r="H23">
-        <v>20260618</v>
-      </c>
-      <c r="I23">
-        <v>20260620</v>
-      </c>
-      <c r="J23">
-        <v>30</v>
-      </c>
-      <c r="K23">
-        <v>2</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23">
-        <v>1</v>
-      </c>
-      <c r="N23">
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" t="s">
-        <v>78</v>
-      </c>
-      <c r="D24">
-        <v>877657</v>
-      </c>
-      <c r="E24" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24">
-        <v>7</v>
       </c>
       <c r="H24">
         <v>20260618</v>
@@ -1841,10 +1876,10 @@
         <v>20260620</v>
       </c>
       <c r="J24">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24">
         <v>1</v>
@@ -1859,21 +1894,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>51</v>
+    <row r="25" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C25" t="s">
         <v>78</v>
       </c>
       <c r="D25">
-        <v>880000</v>
+        <v>877657</v>
       </c>
       <c r="E25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
         <v>21</v>
@@ -1882,239 +1917,239 @@
         <v>7</v>
       </c>
       <c r="H25">
+        <v>20260618</v>
+      </c>
+      <c r="I25">
+        <v>20260620</v>
+      </c>
+      <c r="J25">
+        <v>47</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26">
+        <v>880000</v>
+      </c>
+      <c r="E26" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26">
+        <v>7</v>
+      </c>
+      <c r="H26">
         <v>20260617</v>
       </c>
-      <c r="I25">
-        <v>20260620</v>
-      </c>
-      <c r="J25">
+      <c r="I26">
+        <v>20260620</v>
+      </c>
+      <c r="J26">
         <v>49</v>
       </c>
-      <c r="K25">
+      <c r="K26">
         <v>6</v>
       </c>
-      <c r="L25">
-        <v>1</v>
-      </c>
-      <c r="M25">
-        <v>1</v>
-      </c>
-      <c r="N25">
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26">
+      <c r="L26">
+        <v>1</v>
+      </c>
+      <c r="M26">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27">
         <v>881691</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>68</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>15</v>
       </c>
-      <c r="G26">
+      <c r="G27">
         <v>8</v>
       </c>
-      <c r="H26">
+      <c r="H27">
         <v>20260519</v>
       </c>
-      <c r="I26">
-        <v>20260620</v>
-      </c>
-      <c r="J26">
+      <c r="I27">
+        <v>20260620</v>
+      </c>
+      <c r="J27">
         <v>514</v>
       </c>
-      <c r="K26">
+      <c r="K27">
         <v>17</v>
       </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26">
-        <v>1</v>
-      </c>
-      <c r="N26">
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27">
+      <c r="L27">
+        <v>1</v>
+      </c>
+      <c r="M27">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28">
         <v>882013</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>43</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>25</v>
       </c>
-      <c r="G27">
+      <c r="G28">
         <v>10</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>20260522</v>
       </c>
-      <c r="I27">
-        <v>20260620</v>
-      </c>
-      <c r="J27">
+      <c r="I28">
+        <v>20260620</v>
+      </c>
+      <c r="J28">
         <v>677</v>
       </c>
-      <c r="K27">
-        <v>1</v>
-      </c>
-      <c r="L27">
-        <v>1</v>
-      </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
-      <c r="N27">
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" t="s">
-        <v>78</v>
-      </c>
-      <c r="D28">
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="O28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29">
         <v>882320</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>44</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>16</v>
       </c>
-      <c r="G28">
+      <c r="G29">
         <v>9</v>
       </c>
-      <c r="H28">
+      <c r="H29">
         <v>20260612</v>
       </c>
-      <c r="I28">
-        <v>20260620</v>
-      </c>
-      <c r="J28">
+      <c r="I29">
+        <v>20260620</v>
+      </c>
+      <c r="J29">
         <v>169</v>
       </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>1</v>
-      </c>
-      <c r="N28">
-        <v>1</v>
-      </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29">
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>1</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D30">
         <v>883370</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>45</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>21</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>7</v>
-      </c>
-      <c r="H29">
-        <v>20260617</v>
-      </c>
-      <c r="I29">
-        <v>20260620</v>
-      </c>
-      <c r="J29">
-        <v>53</v>
-      </c>
-      <c r="K29">
-        <v>3</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" t="s">
-        <v>78</v>
-      </c>
-      <c r="D30">
-        <v>883409</v>
-      </c>
-      <c r="E30" t="s">
-        <v>80</v>
-      </c>
-      <c r="F30" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30">
-        <v>10</v>
       </c>
       <c r="H30">
         <v>20260617</v>
@@ -2123,587 +2158,587 @@
         <v>20260620</v>
       </c>
       <c r="J30">
+        <v>53</v>
+      </c>
+      <c r="K30">
+        <v>3</v>
+      </c>
+      <c r="L30">
+        <v>1</v>
+      </c>
+      <c r="M30">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="O30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>78</v>
+      </c>
+      <c r="D31">
+        <v>883409</v>
+      </c>
+      <c r="E31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F31" t="s">
+        <v>25</v>
+      </c>
+      <c r="G31">
+        <v>10</v>
+      </c>
+      <c r="H31">
+        <v>20260617</v>
+      </c>
+      <c r="I31">
+        <v>20260620</v>
+      </c>
+      <c r="J31">
         <v>91</v>
       </c>
-      <c r="K30">
+      <c r="K31">
         <v>2</v>
       </c>
-      <c r="L30">
-        <v>1</v>
-      </c>
-      <c r="M30">
-        <v>1</v>
-      </c>
-      <c r="N30">
-        <v>1</v>
-      </c>
-      <c r="O30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D31">
+      <c r="L31">
+        <v>1</v>
+      </c>
+      <c r="M31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="O31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32">
         <v>883671</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>46</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" t="s">
         <v>16</v>
       </c>
-      <c r="G31">
+      <c r="G32">
         <v>9</v>
       </c>
-      <c r="H31">
+      <c r="H32">
         <v>20260608</v>
       </c>
-      <c r="I31">
-        <v>20260620</v>
-      </c>
-      <c r="J31">
+      <c r="I32">
+        <v>20260620</v>
+      </c>
+      <c r="J32">
         <v>167</v>
       </c>
-      <c r="K31">
-        <v>1</v>
-      </c>
-      <c r="L31">
-        <v>1</v>
-      </c>
-      <c r="M31">
-        <v>1</v>
-      </c>
-      <c r="N31">
-        <v>1</v>
-      </c>
-      <c r="O31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C32" t="s">
-        <v>78</v>
-      </c>
-      <c r="D32">
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>1</v>
+      </c>
+      <c r="M32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="O32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33">
         <v>883846</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>47</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F33" t="s">
         <v>13</v>
-      </c>
-      <c r="G32">
-        <v>6</v>
-      </c>
-      <c r="H32">
-        <v>20260610</v>
-      </c>
-      <c r="I32">
-        <v>20260620</v>
-      </c>
-      <c r="J32">
-        <v>205</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32">
-        <v>1</v>
-      </c>
-      <c r="N32">
-        <v>1</v>
-      </c>
-      <c r="O32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C33" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33">
-        <v>884123</v>
-      </c>
-      <c r="E33" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" t="s">
-        <v>18</v>
       </c>
       <c r="G33">
         <v>6</v>
       </c>
       <c r="H33">
+        <v>20260610</v>
+      </c>
+      <c r="I33">
+        <v>20260620</v>
+      </c>
+      <c r="J33">
+        <v>205</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="M33">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34">
+        <v>884123</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34">
         <v>20260612</v>
       </c>
-      <c r="I33">
-        <v>20260620</v>
-      </c>
-      <c r="J33">
+      <c r="I34">
+        <v>20260620</v>
+      </c>
+      <c r="J34">
         <v>180</v>
       </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-      <c r="L33">
-        <v>1</v>
-      </c>
-      <c r="M33">
-        <v>1</v>
-      </c>
-      <c r="N33">
-        <v>1</v>
-      </c>
-      <c r="O33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34">
+      <c r="K34">
+        <v>1</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="M34">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="O34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D35">
         <v>884357</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E35" t="s">
         <v>49</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>16</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <v>8</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <v>20260615</v>
       </c>
-      <c r="I34">
-        <v>20260620</v>
-      </c>
-      <c r="J34">
+      <c r="I35">
+        <v>20260620</v>
+      </c>
+      <c r="J35">
         <v>68</v>
       </c>
-      <c r="K34">
+      <c r="K35">
         <v>5</v>
       </c>
-      <c r="L34">
-        <v>1</v>
-      </c>
-      <c r="M34">
-        <v>1</v>
-      </c>
-      <c r="N34">
-        <v>1</v>
-      </c>
-      <c r="O34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35" t="s">
-        <v>78</v>
-      </c>
-      <c r="D35">
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>1</v>
+      </c>
+      <c r="O35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36">
         <v>884642</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E36" t="s">
         <v>70</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" t="s">
         <v>25</v>
       </c>
-      <c r="G35">
+      <c r="G36">
         <v>10</v>
       </c>
-      <c r="H35">
+      <c r="H36">
         <v>20260617</v>
       </c>
-      <c r="I35">
-        <v>20260620</v>
-      </c>
-      <c r="J35">
+      <c r="I36">
+        <v>20260620</v>
+      </c>
+      <c r="J36">
         <v>104</v>
       </c>
-      <c r="K35">
-        <v>1</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35">
-        <v>1</v>
-      </c>
-      <c r="N35">
-        <v>1</v>
-      </c>
-      <c r="O35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>51</v>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36">
+        <v>1</v>
+      </c>
+      <c r="M36">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="O36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C37" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>51</v>
+    <row r="38" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C38" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>51</v>
+    <row r="39" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C39" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>51</v>
+    <row r="40" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C40" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>51</v>
+    <row r="41" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C41" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>51</v>
+    <row r="42" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C42" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>51</v>
+    <row r="43" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C43" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>51</v>
+    <row r="44" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C44" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>51</v>
+    <row r="45" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C45" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>51</v>
+    <row r="46" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C46" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>51</v>
+    <row r="47" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C47" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>51</v>
+    <row r="48" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C48" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>51</v>
+    <row r="49" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C49" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>51</v>
+    <row r="50" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C50" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>51</v>
+    <row r="51" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C51" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>51</v>
+    <row r="52" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>51</v>
+    <row r="53" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C53" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>51</v>
+    <row r="54" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C54" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>51</v>
+    <row r="55" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C55" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>51</v>
+    <row r="56" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C56" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>51</v>
+    <row r="57" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C57" t="s">
         <v>78</v>
       </c>
-      <c r="D57" s="6"/>
-    </row>
-    <row r="58" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>51</v>
+      <c r="D57" s="5"/>
+    </row>
+    <row r="58" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C58" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>51</v>
+    <row r="59" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C59" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>51</v>
+    <row r="60" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C60" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>51</v>
+    <row r="61" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C61" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="2"/>
-      <c r="D62" t="s">
-        <v>0</v>
-      </c>
-      <c r="E62" t="s">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>2</v>
-      </c>
-      <c r="G62" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" t="s">
-        <v>4</v>
-      </c>
-      <c r="I62" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" t="s">
-        <v>6</v>
-      </c>
-      <c r="K62" t="s">
-        <v>7</v>
-      </c>
-      <c r="L62" t="s">
-        <v>8</v>
-      </c>
-      <c r="M62" t="s">
-        <v>9</v>
-      </c>
-      <c r="N62" t="s">
-        <v>10</v>
-      </c>
-      <c r="O62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>52</v>
       </c>
@@ -2797,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>52</v>
       </c>
@@ -2985,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>52</v>
       </c>
@@ -3173,7 +3208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>52</v>
       </c>
@@ -3184,28 +3219,28 @@
         <v>73</v>
       </c>
       <c r="D73">
-        <v>670691</v>
+        <v>636751</v>
       </c>
       <c r="E73" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F73" t="s">
         <v>13</v>
       </c>
       <c r="G73">
+        <v>51</v>
+      </c>
+      <c r="H73">
+        <v>20260620</v>
+      </c>
+      <c r="I73">
+        <v>20260620</v>
+      </c>
+      <c r="J73">
+        <v>19</v>
+      </c>
+      <c r="K73">
         <v>8</v>
-      </c>
-      <c r="H73">
-        <v>20260518</v>
-      </c>
-      <c r="I73">
-        <v>20260620</v>
-      </c>
-      <c r="J73">
-        <v>670</v>
-      </c>
-      <c r="K73">
-        <v>6</v>
       </c>
       <c r="L73">
         <v>1</v>
@@ -3231,28 +3266,28 @@
         <v>73</v>
       </c>
       <c r="D74">
-        <v>716266</v>
+        <v>670691</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F74" t="s">
         <v>13</v>
       </c>
       <c r="G74">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="H74">
-        <v>20260519</v>
+        <v>20260518</v>
       </c>
       <c r="I74">
         <v>20260620</v>
       </c>
       <c r="J74">
-        <v>541</v>
+        <v>670</v>
       </c>
       <c r="K74">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L74">
         <v>1</v>
@@ -3267,7 +3302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>52</v>
       </c>
@@ -3278,28 +3313,28 @@
         <v>73</v>
       </c>
       <c r="D75">
-        <v>784496</v>
+        <v>716266</v>
       </c>
       <c r="E75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F75" t="s">
         <v>13</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="H75">
-        <v>20260616</v>
+        <v>20260519</v>
       </c>
       <c r="I75">
         <v>20260620</v>
       </c>
       <c r="J75">
-        <v>96</v>
+        <v>541</v>
       </c>
       <c r="K75">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L75">
         <v>1</v>
@@ -3314,7 +3349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>52</v>
       </c>
@@ -3325,28 +3360,28 @@
         <v>73</v>
       </c>
       <c r="D76">
-        <v>853015</v>
+        <v>784496</v>
       </c>
       <c r="E76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F76" t="s">
         <v>13</v>
       </c>
       <c r="G76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76">
-        <v>20260604</v>
+        <v>20260616</v>
       </c>
       <c r="I76">
         <v>20260620</v>
       </c>
       <c r="J76">
-        <v>388</v>
+        <v>96</v>
       </c>
       <c r="K76">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L76">
         <v>1</v>
@@ -3361,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>52</v>
       </c>
@@ -3372,28 +3407,28 @@
         <v>73</v>
       </c>
       <c r="D77">
-        <v>877549</v>
+        <v>795757</v>
       </c>
       <c r="E77" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F77" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G77">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H77">
-        <v>20260408</v>
+        <v>20260620</v>
       </c>
       <c r="I77">
         <v>20260620</v>
       </c>
       <c r="J77">
-        <v>1192</v>
+        <v>18</v>
       </c>
       <c r="K77">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L77">
         <v>1</v>
@@ -3419,28 +3454,28 @@
         <v>73</v>
       </c>
       <c r="D78">
-        <v>879845</v>
+        <v>853015</v>
       </c>
       <c r="E78" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F78" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G78">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="H78">
-        <v>20260501</v>
+        <v>20260604</v>
       </c>
       <c r="I78">
         <v>20260620</v>
       </c>
       <c r="J78">
-        <v>1379</v>
+        <v>388</v>
       </c>
       <c r="K78">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L78">
         <v>1</v>
@@ -3455,7 +3490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>52</v>
       </c>
@@ -3466,28 +3501,28 @@
         <v>73</v>
       </c>
       <c r="D79">
-        <v>879846</v>
+        <v>877549</v>
       </c>
       <c r="E79" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G79">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H79">
-        <v>20260506</v>
+        <v>20260408</v>
       </c>
       <c r="I79">
         <v>20260620</v>
       </c>
       <c r="J79">
-        <v>1942</v>
+        <v>1192</v>
       </c>
       <c r="K79">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L79">
         <v>1</v>
@@ -3502,7 +3537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>52</v>
       </c>
@@ -3513,28 +3548,28 @@
         <v>73</v>
       </c>
       <c r="D80">
-        <v>884003</v>
+        <v>879845</v>
       </c>
       <c r="E80" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G80">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="H80">
-        <v>20260615</v>
+        <v>20260501</v>
       </c>
       <c r="I80">
         <v>20260620</v>
       </c>
       <c r="J80">
-        <v>62</v>
+        <v>1379</v>
       </c>
       <c r="K80">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L80">
         <v>1</v>
@@ -3560,28 +3595,28 @@
         <v>73</v>
       </c>
       <c r="D81">
-        <v>884749</v>
+        <v>879846</v>
       </c>
       <c r="E81" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F81" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G81">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H81">
-        <v>20260618</v>
+        <v>20260506</v>
       </c>
       <c r="I81">
         <v>20260620</v>
       </c>
       <c r="J81">
-        <v>93</v>
+        <v>1942</v>
       </c>
       <c r="K81">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L81">
         <v>1</v>
@@ -3607,28 +3642,28 @@
         <v>73</v>
       </c>
       <c r="D82">
-        <v>884776</v>
+        <v>884003</v>
       </c>
       <c r="E82" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G82">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="H82">
-        <v>20260618</v>
+        <v>20260615</v>
       </c>
       <c r="I82">
         <v>20260620</v>
       </c>
       <c r="J82">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="K82">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L82">
         <v>1</v>
@@ -3654,28 +3689,28 @@
         <v>73</v>
       </c>
       <c r="D83">
-        <v>884895</v>
+        <v>884749</v>
       </c>
       <c r="E83" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F83" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G83">
         <v>51</v>
       </c>
       <c r="H83">
-        <v>20260620</v>
+        <v>20260618</v>
       </c>
       <c r="I83">
         <v>20260620</v>
       </c>
       <c r="J83">
-        <v>15</v>
+        <v>93</v>
       </c>
       <c r="K83">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L83">
         <v>1</v>
@@ -3690,7 +3725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>52</v>
       </c>
@@ -3700,8 +3735,44 @@
       <c r="C84" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <v>884776</v>
+      </c>
+      <c r="E84" t="s">
+        <v>72</v>
+      </c>
+      <c r="F84" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84">
+        <v>51</v>
+      </c>
+      <c r="H84">
+        <v>20260618</v>
+      </c>
+      <c r="I84">
+        <v>20260620</v>
+      </c>
+      <c r="J84">
+        <v>42</v>
+      </c>
+      <c r="K84">
+        <v>10</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>1</v>
+      </c>
+      <c r="O84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>52</v>
       </c>
@@ -3711,8 +3782,44 @@
       <c r="C85" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <v>884864</v>
+      </c>
+      <c r="E85" t="s">
+        <v>85</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+      <c r="G85">
+        <v>11</v>
+      </c>
+      <c r="H85">
+        <v>20260619</v>
+      </c>
+      <c r="I85">
+        <v>20260620</v>
+      </c>
+      <c r="J85">
+        <v>55</v>
+      </c>
+      <c r="K85">
+        <v>2</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>52</v>
       </c>
@@ -3722,8 +3829,44 @@
       <c r="C86" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <v>884895</v>
+      </c>
+      <c r="E86" t="s">
+        <v>82</v>
+      </c>
+      <c r="F86" t="s">
+        <v>23</v>
+      </c>
+      <c r="G86">
+        <v>51</v>
+      </c>
+      <c r="H86">
+        <v>20260620</v>
+      </c>
+      <c r="I86">
+        <v>20260620</v>
+      </c>
+      <c r="J86">
+        <v>15</v>
+      </c>
+      <c r="K86">
+        <v>8</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>52</v>
       </c>
@@ -3733,8 +3876,44 @@
       <c r="C87" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" ht="17.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <v>884936</v>
+      </c>
+      <c r="E87" t="s">
+        <v>86</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+      <c r="G87">
+        <v>51</v>
+      </c>
+      <c r="H87">
+        <v>20260620</v>
+      </c>
+      <c r="I87">
+        <v>20260620</v>
+      </c>
+      <c r="J87">
+        <v>33</v>
+      </c>
+      <c r="K87">
+        <v>13</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>52</v>
       </c>
@@ -3746,14 +3925,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O88">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="51"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:O88"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>